--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_272_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_272_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9391</v>
+        <v>4.1825</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5981</v>
+        <v>2.9087</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3411</v>
+        <v>1.2739</v>
       </c>
       <c r="G2" t="n">
         <v>2.8242</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0448</v>
+        <v>0.1986</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1336</v>
+        <v>0.177</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0887</v>
+        <v>0.0215</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8789</v>
+        <v>2.8693</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5007</v>
       </c>
       <c r="F3" t="n">
-        <v>2.335</v>
+        <v>2.3686</v>
       </c>
       <c r="G3" t="n">
         <v>2.166</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2464</v>
+        <v>0.2368</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3541</v>
+        <v>0.3108</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1076</v>
+        <v>-0.074</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7482</v>
+        <v>1.4487</v>
       </c>
       <c r="E4" t="n">
-        <v>0.222</v>
+        <v>1.9744</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5262</v>
+        <v>-0.5256</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.268</v>
+        <v>2.3917</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7503</v>
+        <v>1.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4822</v>
+        <v>1.2883</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9832</v>
+        <v>3.9683</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9271</v>
+        <v>2.2519</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9103</v>
+        <v>1.7164</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2512</v>
+        <v>-1.5765</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-1.1484</v>
       </c>
       <c r="O4" t="n">
         <v>-0.4281</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1076</v>
+        <v>-1.4095</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4753</v>
+        <v>-0.7466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3677</v>
+        <v>-0.6629</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8919</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0336</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7917999999999999</v>
+        <v>1.3023</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3846</v>
+        <v>0.4147</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5928</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3917</v>
+        <v>-0.268</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1034</v>
+        <v>-1.7503</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2883</v>
+        <v>1.4822</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9683</v>
+        <v>0.9832</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2519</v>
+        <v>-0.9271</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7164</v>
+        <v>1.9103</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5765</v>
+        <v>-1.2512</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1484</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>-0.4281</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0665</v>
+        <v>-0.5535</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3364</v>
+        <v>-0.2827</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7301</v>
+        <v>-0.2708</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9304</v>
+        <v>1.8919</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>2.0336</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.447</v>
+        <v>0.5198</v>
       </c>
       <c r="E6" t="n">
-        <v>0.834</v>
+        <v>1.3719</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.387</v>
+        <v>-0.8522</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2473</v>
+        <v>2.3947</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.2051</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6591</v>
+        <v>2.5998</v>
       </c>
       <c r="J6" t="n">
-        <v>0.49</v>
+        <v>3.2494</v>
       </c>
       <c r="K6" t="n">
-        <v>0.306</v>
+        <v>0.8571</v>
       </c>
       <c r="L6" t="n">
-        <v>0.184</v>
+        <v>2.3923</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7373</v>
+        <v>-0.8547</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8942</v>
+        <v>-1.0622</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8431</v>
+        <v>0.2075</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.854</v>
+        <v>-0.4806</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8259</v>
+        <v>0.0709</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0281</v>
+        <v>-0.5515</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.7886</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4456</v>
+        <v>0.4019</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3164</v>
+        <v>-0.3985</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8708</v>
+        <v>0.8004</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0346</v>
+        <v>1.1154</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8006</v>
+        <v>-1.0359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.766</v>
+        <v>2.1513</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3304</v>
+        <v>2.0592</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1779</v>
+        <v>-0.4131</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5082</v>
+        <v>2.4723</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.365</v>
+        <v>-0.9438</v>
       </c>
       <c r="N7" t="n">
         <v>-0.6227</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2578</v>
+        <v>-0.3211</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1581</v>
+        <v>-0.7677</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0736</v>
+        <v>-0.1924</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9155</v>
+        <v>-0.5753</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0693</v>
+        <v>0.0143</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0181</v>
+        <v>0.6834</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0874</v>
+        <v>-0.6692</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3947</v>
+        <v>-0.0346</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2051</v>
+        <v>-0.8006</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5998</v>
+        <v>0.766</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2494</v>
+        <v>0.3304</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8571</v>
+        <v>-0.1779</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3923</v>
+        <v>0.5082</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8547</v>
+        <v>-0.365</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0622</v>
+        <v>-0.6227</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2075</v>
+        <v>0.2578</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0697</v>
+        <v>-0.2732</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2829</v>
+        <v>0.4406</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.7139</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9304</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5142</v>
+        <v>-0.5131</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.945</v>
+        <v>0.0083</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4308</v>
+        <v>-0.5215</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1154</v>
+        <v>-1.2473</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0359</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1513</v>
+        <v>-0.6591</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0592</v>
+        <v>0.49</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4131</v>
+        <v>0.306</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4723</v>
+        <v>0.184</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9438</v>
+        <v>-1.7373</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6227</v>
+        <v>-0.8942</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3211</v>
+        <v>-0.8431</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.4793</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6838</v>
+        <v>-0.1061</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>0.0002</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9449</v>
+        <v>-0.1063</v>
       </c>
       <c r="V9" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3588</v>
+        <v>-1.4596</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6352</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7237</v>
+        <v>-0.8245</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0414</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3897</v>
+        <v>-0.4905</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3229</v>
+        <v>-0.4237</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5575</v>
+        <v>-1.5068</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1094</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4481</v>
+        <v>-0.5154</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5152</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0299</v>
+        <v>0.0806</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0158</v>
+        <v>0.1338</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8383</v>
+        <v>-1.9734</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4688</v>
+        <v>-0.7047</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3696</v>
+        <v>-1.2688</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1609</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2315</v>
+        <v>-0.3666</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.271</v>
+        <v>-0.1702</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.912500000000001</v>
+        <v>5.285900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>4.758700000000001</v>
+        <v>5.132300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1537000000000002</v>
+        <v>0.1533</v>
       </c>
       <c r="G13" t="n">
         <v>6.624599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3052</v>
+        <v>-3.9317</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.725</v>
+        <v>-0.3516000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.5802</v>
+        <v>-3.5803</v>
       </c>
       <c r="V13" t="n">
         <v>3.752699999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6824</v>
+        <v>2.7441</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3316</v>
+        <v>1.5682</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3507</v>
+        <v>1.176</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4428</v>
+        <v>1.9867</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6062</v>
+        <v>2.7129</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8366</v>
+        <v>-0.7262</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1427</v>
+        <v>3.5413</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1427</v>
+        <v>3.3141</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.2272</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3001</v>
+        <v>-1.5546</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5365</v>
+        <v>-0.6012</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8366</v>
+        <v>-0.9534</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1494</v>
+        <v>1.0616</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1889</v>
+        <v>0.5783</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0395</v>
+        <v>0.4832</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.571</v>
+        <v>2.643</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9784</v>
+        <v>0.9778</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5926</v>
+        <v>1.6653</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9867</v>
+        <v>1.4428</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7129</v>
+        <v>0.6062</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7262</v>
+        <v>0.8366</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5413</v>
+        <v>1.1427</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3141</v>
+        <v>1.1427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5546</v>
+        <v>0.3001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6012</v>
+        <v>-0.5365</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9534</v>
+        <v>0.8366</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1116</v>
+        <v>0.11</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0114</v>
+        <v>-0.165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1002</v>
+        <v>0.275</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.292</v>
+        <v>2.1456</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2943</v>
+        <v>0.1775</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5863</v>
+        <v>1.968</v>
       </c>
       <c r="G16" t="n">
         <v>0.8401999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.427</v>
+        <v>0.4266</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1625</v>
+        <v>0.5443</v>
       </c>
       <c r="V16" t="n">
         <v>0.6468</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1264</v>
+        <v>0.8448</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0393</v>
+        <v>2.3315</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9128</v>
+        <v>-1.4867</v>
       </c>
       <c r="G17" t="n">
         <v>0.3897</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2212</v>
+        <v>0.9397</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5138</v>
+        <v>0.8061</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2926</v>
+        <v>0.1336</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2525</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3739</v>
+        <v>0.4373</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5671</v>
+        <v>-0.2133</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.6506</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3918</v>
@@ -1858,13 +1858,13 @@
         <v>2.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0903</v>
+        <v>1.1538</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0633</v>
+        <v>0.4171</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0271</v>
+        <v>0.7367</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7886</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2743</v>
+        <v>-1.0157</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7895</v>
+        <v>1.0818</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0639</v>
+        <v>-2.0975</v>
       </c>
       <c r="G19" t="n">
         <v>1.1033</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1611</v>
+        <v>0.4197</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0499</v>
+        <v>0.3422</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1111</v>
+        <v>0.0775</v>
       </c>
       <c r="V19" t="n">
         <v>-2.5387</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7146</v>
+        <v>-2.0292</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1149</v>
+        <v>-0.357</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8295</v>
+        <v>-1.6722</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3081</v>
@@ -2014,13 +2014,13 @@
         <v>3.0154</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7379</v>
+        <v>1.4233</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5613</v>
+        <v>1.0895</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1766</v>
+        <v>0.3339</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.813</v>
+        <v>-2.2289</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9742</v>
+        <v>-1.7383</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8388</v>
+        <v>-0.4906</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3715</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0224</v>
+        <v>0.6065</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2794</v>
+        <v>0.5153</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.257</v>
+        <v>0.0912</v>
       </c>
       <c r="V21" t="n">
         <v>1.6083</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4293</v>
+        <v>-2.8568</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6222</v>
+        <v>-1.0595</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8071</v>
+        <v>-1.7974</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3409</v>
+        <v>-2.9752</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3421</v>
+        <v>-1.0815</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.683</v>
+        <v>-1.8936</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0707</v>
+        <v>0.0803</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8571</v>
+        <v>-0.0301</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7863</v>
+        <v>0.1104</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4116</v>
+        <v>-3.0555</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5149</v>
+        <v>-1.0514</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8966</v>
+        <v>-2.004</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2328</v>
+        <v>0.5643</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>0.2519</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1406</v>
+        <v>0.3123</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7269</v>
+        <v>-3.2378</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4133</v>
+        <v>-2.3863</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3135</v>
+        <v>-0.8515</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9752</v>
+        <v>-1.3409</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0815</v>
+        <v>0.3421</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8936</v>
+        <v>-1.683</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0803</v>
+        <v>0.0707</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0301</v>
+        <v>0.8571</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1104</v>
+        <v>-0.7863</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0555</v>
+        <v>-1.4116</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0514</v>
+        <v>-0.5149</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.004</v>
+        <v>-0.8966</v>
       </c>
       <c r="P23" t="n">
-        <v>0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3058</v>
+        <v>-0.0413</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1019</v>
+        <v>-0.1375</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2038</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9124</v>
+        <v>-2.553599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3826000000000001</v>
+        <v>0.382400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.295</v>
+        <v>-2.936</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6248</v>
@@ -2296,7 +2296,7 @@
         <v>2.0578</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.682499999999999</v>
+        <v>-8.682500000000001</v>
       </c>
       <c r="J24" t="n">
         <v>8.206099999999999</v>
@@ -2326,13 +2326,13 @@
         <v>16.2367</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3051</v>
+        <v>6.6642</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5804</v>
+        <v>3.5802</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7247999999999999</v>
+        <v>3.0839</v>
       </c>
       <c r="V24" t="n">
         <v>-3.7527</v>
